--- a/output/sales_report.xlsx
+++ b/output/sales_report.xlsx
@@ -44,7 +44,7 @@
     <t>Unique Customers</t>
   </si>
   <si>
-    <t>Average Order Value</t>
+    <t>Average Transaction Value</t>
   </si>
   <si>
     <t>Best Selling Product</t>
